--- a/r4-ELGA-AustrianPatientSummary-55-56---create-examples-for-each-at-aps-profile/StructureDefinition-at-aps-medicationdispense.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-55-56---create-examples-for-each-at-aps-profile/StructureDefinition-at-aps-medicationdispense.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1724" uniqueCount="371">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1724" uniqueCount="369">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-11T12:31:41+00:00</t>
+    <t>2026-01-28T09:02:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -499,7 +499,7 @@
     <t>MedicationDispense.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Procedure|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-procedure)
 </t>
   </si>
   <si>
@@ -604,8 +604,8 @@
     <t>MedicationDispense.medication[x]</t>
   </si>
   <si>
-    <t>CodeableConcept
-Reference(Medication|4.0.1)</t>
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-medication)
+</t>
   </si>
   <si>
     <t>What medication was supplied</t>
@@ -615,12 +615,6 @@
   </si>
   <si>
     <t>If only a code is specified, then it needs to be a code for a specific product. If more information is required, then the use of the medication resource is recommended.  For example, if you require form or lot number, then you must reference the Medication resource.</t>
-  </si>
-  <si>
-    <t>A coded concept identifying which substance or product can be dispensed.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-codes|4.0.1</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -792,7 +786,7 @@
     <t>MedicationDispense.performer.actor</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1|Patient|4.0.1|Device|4.0.1|RelatedPerson|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-practitioner|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-practitionerrole|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-organization|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-patient|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-device|RelatedPerson)
 </t>
   </si>
   <si>
@@ -827,7 +821,7 @@
     <t>MedicationDispense.authorizingPrescription</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationRequest|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-medicationrequest)
 </t>
   </si>
   <si>
@@ -971,7 +965,7 @@
     <t>MedicationDispense.receiver</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|4.0.1|Practitioner|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-patient|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-practitioner)
 </t>
   </si>
   <si>
@@ -1114,7 +1108,7 @@
     <t>MedicationDispense.substitution.responsibleParty</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-practitioner|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-practitionerrole)
 </t>
   </si>
   <si>
@@ -1492,7 +1486,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="93.98828125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -3344,13 +3338,13 @@
         <v>79</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>176</v>
+        <v>79</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>194</v>
+        <v>79</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>195</v>
+        <v>79</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>79</v>
@@ -3383,27 +3377,27 @@
         <v>101</v>
       </c>
       <c r="AK16" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="AL16" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="AM16" t="s" s="2">
         <v>196</v>
       </c>
-      <c r="AL16" t="s" s="2">
+      <c r="AN16" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="AM16" t="s" s="2">
+      <c r="AO16" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="AN16" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="AO16" t="s" s="2">
-        <v>200</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3426,16 +3420,16 @@
         <v>90</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="L17" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>205</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3485,7 +3479,7 @@
         <v>79</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -3500,27 +3494,27 @@
         <v>101</v>
       </c>
       <c r="AK17" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="AL17" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="AM17" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="AL17" t="s" s="2">
+      <c r="AN17" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO17" t="s" s="2">
         <v>207</v>
-      </c>
-      <c r="AM17" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="AN17" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO17" t="s" s="2">
-        <v>209</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3543,13 +3537,13 @@
         <v>79</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="L18" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>211</v>
-      </c>
-      <c r="L18" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>213</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3600,7 +3594,7 @@
         <v>79</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -3615,10 +3609,10 @@
         <v>101</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>79</v>
@@ -3632,10 +3626,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3658,13 +3652,13 @@
         <v>79</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>217</v>
-      </c>
-      <c r="L19" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>219</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3715,7 +3709,7 @@
         <v>79</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -3733,10 +3727,10 @@
         <v>79</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>79</v>
@@ -3747,10 +3741,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3773,13 +3767,13 @@
         <v>79</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="L20" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>225</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3830,7 +3824,7 @@
         <v>79</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -3845,10 +3839,10 @@
         <v>101</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>79</v>
@@ -3862,10 +3856,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3888,13 +3882,13 @@
         <v>79</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="L21" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="L21" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>231</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3945,7 +3939,7 @@
         <v>79</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -3963,7 +3957,7 @@
         <v>79</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>79</v>
@@ -3977,10 +3971,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4009,7 +4003,7 @@
         <v>136</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="N22" t="s" s="2">
         <v>138</v>
@@ -4062,7 +4056,7 @@
         <v>79</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4080,7 +4074,7 @@
         <v>79</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>79</v>
@@ -4094,14 +4088,14 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4123,10 +4117,10 @@
         <v>135</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="N23" t="s" s="2">
         <v>138</v>
@@ -4181,7 +4175,7 @@
         <v>79</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4213,10 +4207,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4242,14 +4236,14 @@
         <v>182</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>79</v>
@@ -4277,10 +4271,10 @@
         <v>176</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>79</v>
@@ -4298,7 +4292,7 @@
         <v>79</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -4316,7 +4310,7 @@
         <v>79</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>79</v>
@@ -4330,10 +4324,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4356,13 +4350,13 @@
         <v>79</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="L25" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>250</v>
-      </c>
-      <c r="L25" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>252</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4413,7 +4407,7 @@
         <v>79</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>89</v>
@@ -4428,10 +4422,10 @@
         <v>101</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>79</v>
@@ -4445,10 +4439,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4471,13 +4465,13 @@
         <v>79</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="L26" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4528,7 +4522,7 @@
         <v>79</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4546,7 +4540,7 @@
         <v>79</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>79</v>
@@ -4560,10 +4554,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4586,16 +4580,16 @@
         <v>79</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>264</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4645,7 +4639,7 @@
         <v>79</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -4660,27 +4654,27 @@
         <v>101</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="AL27" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="AM27" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN27" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="AL27" t="s" s="2">
+      <c r="AO27" t="s" s="2">
         <v>266</v>
-      </c>
-      <c r="AM27" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="AO27" t="s" s="2">
-        <v>268</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4706,10 +4700,10 @@
         <v>182</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4739,10 +4733,10 @@
         <v>176</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>79</v>
@@ -4760,7 +4754,7 @@
         <v>79</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -4778,24 +4772,24 @@
         <v>79</v>
       </c>
       <c r="AL28" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="AM28" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN28" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="AO28" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="AM28" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="AO28" t="s" s="2">
-        <v>275</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4818,13 +4812,13 @@
         <v>79</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>277</v>
-      </c>
-      <c r="L29" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>279</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4875,7 +4869,7 @@
         <v>79</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -4893,24 +4887,24 @@
         <v>79</v>
       </c>
       <c r="AL29" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="AM29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN29" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="AO29" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="AO29" t="s" s="2">
-        <v>282</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4933,13 +4927,13 @@
         <v>79</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4990,7 +4984,7 @@
         <v>79</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5008,7 +5002,7 @@
         <v>79</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>79</v>
@@ -5017,15 +5011,15 @@
         <v>79</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5048,13 +5042,13 @@
         <v>90</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="L31" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>291</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5105,7 +5099,7 @@
         <v>79</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5123,24 +5117,24 @@
         <v>79</v>
       </c>
       <c r="AL31" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="AM31" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN31" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="AO31" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="AM31" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN31" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="AO31" t="s" s="2">
-        <v>294</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5163,13 +5157,13 @@
         <v>79</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5220,7 +5214,7 @@
         <v>79</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5235,27 +5229,27 @@
         <v>101</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5278,13 +5272,13 @@
         <v>79</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5335,7 +5329,7 @@
         <v>79</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5353,24 +5347,24 @@
         <v>79</v>
       </c>
       <c r="AL33" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="AM33" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN33" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AO33" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="AM33" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="AO33" t="s" s="2">
-        <v>305</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5393,13 +5387,13 @@
         <v>79</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="L34" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="L34" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>309</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5450,7 +5444,7 @@
         <v>79</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -5468,13 +5462,13 @@
         <v>79</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>79</v>
@@ -5482,10 +5476,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5508,13 +5502,13 @@
         <v>79</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="L35" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="L35" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>315</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5565,7 +5559,7 @@
         <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -5580,27 +5574,27 @@
         <v>101</v>
       </c>
       <c r="AK35" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AL35" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="AM35" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN35" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO35" t="s" s="2">
         <v>316</v>
-      </c>
-      <c r="AL35" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="AM35" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN35" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO35" t="s" s="2">
-        <v>318</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5623,16 +5617,16 @@
         <v>79</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>323</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5682,7 +5676,7 @@
         <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -5700,7 +5694,7 @@
         <v>79</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>79</v>
@@ -5714,10 +5708,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5740,13 +5734,13 @@
         <v>79</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5797,7 +5791,7 @@
         <v>79</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -5815,13 +5809,13 @@
         <v>79</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>79</v>
@@ -5829,10 +5823,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5855,13 +5849,13 @@
         <v>79</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="L38" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>231</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5912,7 +5906,7 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -5930,7 +5924,7 @@
         <v>79</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>79</v>
@@ -5944,10 +5938,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5976,7 +5970,7 @@
         <v>136</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="N39" t="s" s="2">
         <v>138</v>
@@ -6029,7 +6023,7 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6047,7 +6041,7 @@
         <v>79</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>79</v>
@@ -6061,14 +6055,14 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6090,10 +6084,10 @@
         <v>135</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="N40" t="s" s="2">
         <v>138</v>
@@ -6148,7 +6142,7 @@
         <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6180,10 +6174,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6206,13 +6200,13 @@
         <v>79</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>334</v>
-      </c>
-      <c r="L41" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>336</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6263,7 +6257,7 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>89</v>
@@ -6281,7 +6275,7 @@
         <v>79</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>79</v>
@@ -6295,10 +6289,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6324,10 +6318,10 @@
         <v>182</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6357,10 +6351,10 @@
         <v>176</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>79</v>
@@ -6378,7 +6372,7 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6396,24 +6390,24 @@
         <v>79</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6439,10 +6433,10 @@
         <v>182</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6472,10 +6466,10 @@
         <v>176</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>79</v>
@@ -6493,7 +6487,7 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -6511,13 +6505,13 @@
         <v>79</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>79</v>
@@ -6525,10 +6519,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6551,13 +6545,13 @@
         <v>79</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="L44" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>355</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6608,7 +6602,7 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -6626,13 +6620,13 @@
         <v>79</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>79</v>
@@ -6640,14 +6634,14 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -6666,16 +6660,16 @@
         <v>79</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="N45" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -6725,7 +6719,7 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -6743,7 +6737,7 @@
         <v>79</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>79</v>
@@ -6757,10 +6751,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6783,16 +6777,16 @@
         <v>79</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>369</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6842,7 +6836,7 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -6860,7 +6854,7 @@
         <v>79</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>79</v>
